--- a/data/raw/Transmission_Connected_Wind_Gen_in_Ireland.xlsx
+++ b/data/raw/Transmission_Connected_Wind_Gen_in_Ireland.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\Energy\renewcast-ireland\renewcast_ireland\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\GitHub\Ireland-energy-forecast\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF16C57B-E043-462C-82AE-113B0363BE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D520EFCD-E68E-4BB0-A467-B7D5CE676125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8DF24AB0-6987-48A8-85C2-4B6DAE3F7CC7}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{8DF24AB0-6987-48A8-85C2-4B6DAE3F7CC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Transmission_Connected_Wind_Gen" sheetId="1" r:id="rId1"/>
@@ -1348,6 +1348,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323006D3-DFDE-4001-9262-72B59D8F4B82}">
   <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="32.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -2805,9 +2808,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>15</v>
@@ -2816,13 +2819,13 @@
         <v>16</v>
       </c>
       <c r="D33" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G33" s="10">
         <v>1</v>
@@ -2831,22 +2834,20 @@
         <v>20</v>
       </c>
       <c r="I33" s="10">
-        <v>100</v>
+        <v>79.2</v>
       </c>
       <c r="J33" s="12">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="K33" s="13">
-        <v>42186</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>94</v>
-      </c>
+        <v>41944</v>
+      </c>
+      <c r="L33" s="14"/>
       <c r="M33" s="10" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="N33" s="10">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O33" s="15" t="s">
         <v>28</v>
@@ -2854,7 +2855,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>15</v>
@@ -2866,10 +2867,10 @@
         <v>3</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G34" s="10">
         <v>1</v>
@@ -2878,20 +2879,20 @@
         <v>20</v>
       </c>
       <c r="I34" s="10">
-        <v>79.2</v>
+        <v>36</v>
       </c>
       <c r="J34" s="12">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="K34" s="13">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="L34" s="14"/>
       <c r="M34" s="10" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="N34" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="O34" s="15" t="s">
         <v>28</v>
@@ -2899,7 +2900,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>15</v>
@@ -2911,10 +2912,10 @@
         <v>3</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G35" s="10">
         <v>1</v>
@@ -2923,28 +2924,28 @@
         <v>20</v>
       </c>
       <c r="I35" s="10">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J35" s="12">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K35" s="13">
-        <v>41974</v>
+        <v>42156</v>
       </c>
       <c r="L35" s="14"/>
       <c r="M35" s="10" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="N35" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O35" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>15</v>
@@ -2953,35 +2954,37 @@
         <v>16</v>
       </c>
       <c r="D36" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="10">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="10">
         <v>100</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G36" s="10">
-        <v>1</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="10">
-        <v>20</v>
-      </c>
       <c r="J36" s="12">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K36" s="13">
-        <v>42156</v>
-      </c>
-      <c r="L36" s="14"/>
+        <v>42186</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="M36" s="10" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="N36" s="10">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O36" s="15" t="s">
         <v>28</v>
@@ -3903,7 +3906,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>151</v>
@@ -3914,29 +3917,29 @@
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
       <c r="F57" s="14" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="G57" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I57" s="10">
-        <v>28.8</v>
+        <v>34</v>
       </c>
       <c r="J57" s="12">
-        <v>28.8</v>
+        <v>34</v>
       </c>
       <c r="K57" s="13">
-        <v>44958</v>
+        <v>44927</v>
       </c>
       <c r="L57" s="14"/>
       <c r="M57" s="10" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="N57" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O57" s="15" t="s">
         <v>28</v>
@@ -3944,7 +3947,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>151</v>
@@ -3955,29 +3958,29 @@
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
       <c r="F58" s="14" t="s">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="G58" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>20</v>
       </c>
       <c r="I58" s="10">
-        <v>34</v>
+        <v>28.8</v>
       </c>
       <c r="J58" s="12">
-        <v>34</v>
+        <v>28.8</v>
       </c>
       <c r="K58" s="13">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="L58" s="14"/>
       <c r="M58" s="10" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="N58" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O58" s="15" t="s">
         <v>28</v>
@@ -4024,9 +4027,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="18">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>15</v>
@@ -4037,7 +4040,7 @@
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
       <c r="F60" s="21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G60" s="20">
         <v>1</v>
@@ -4046,28 +4049,28 @@
         <v>20</v>
       </c>
       <c r="I60" s="20">
-        <v>31</v>
+        <v>91.2</v>
       </c>
       <c r="J60" s="22">
-        <v>30.1</v>
+        <v>91.2</v>
       </c>
       <c r="K60" s="23">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="L60" s="21"/>
       <c r="M60" s="20" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="N60" s="20">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O60" s="24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="18">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>15</v>
@@ -4078,7 +4081,7 @@
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G61" s="20">
         <v>1</v>
@@ -4087,20 +4090,20 @@
         <v>20</v>
       </c>
       <c r="I61" s="20">
-        <v>91.2</v>
+        <v>31</v>
       </c>
       <c r="J61" s="22">
-        <v>91.2</v>
+        <v>30.1</v>
       </c>
       <c r="K61" s="23">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="L61" s="21"/>
       <c r="M61" s="20" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="N61" s="20">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O61" s="24" t="s">
         <v>28</v>
@@ -4291,6 +4294,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O66">
+    <sortCondition ref="K2:K66"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>